--- a/docs/Etiquetas cajas/AMI ETIQUETAS CAJA - CODE BARRAS EXTRA TEMPLATE.xlsx
+++ b/docs/Etiquetas cajas/AMI ETIQUETAS CAJA - CODE BARRAS EXTRA TEMPLATE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jordi\Documents\Workspace\Packing List Automation\docs\Etiquetas cajas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC54ED3F-A360-4551-903A-95C1FB2A6473}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B113B613-C999-4564-98ED-975ECB52D152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{02BB6957-E6F7-49EE-B2B6-A2C9861D9CAC}"/>
   </bookViews>
@@ -147,13 +147,13 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -228,13 +228,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>60959</xdr:colOff>
+      <xdr:colOff>22859</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1173952</xdr:colOff>
+      <xdr:colOff>1135852</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>131259</xdr:rowOff>
     </xdr:to>
@@ -266,7 +266,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4777739" y="586740"/>
+          <a:off x="4739639" y="586740"/>
           <a:ext cx="2118833" cy="352239"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -334,13 +334,13 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>68580</xdr:colOff>
+      <xdr:colOff>22860</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1181573</xdr:colOff>
+      <xdr:colOff>1135853</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>116019</xdr:rowOff>
     </xdr:to>
@@ -372,7 +372,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4785360" y="1973580"/>
+          <a:off x="4739640" y="1973580"/>
           <a:ext cx="2118833" cy="352239"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -440,7 +440,7 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
+      <xdr:colOff>30480</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:from>
@@ -473,7 +473,7 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="4770120" y="3375660"/>
+          <a:off x="4747260" y="3375660"/>
           <a:ext cx="2118833" cy="352239"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -811,10 +811,10 @@
   <sheetData>
     <row r="1" spans="1:11" ht="6" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="1"/>
@@ -834,8 +834,8 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
+      <c r="A3" s="5"/>
+      <c r="B3" s="6"/>
       <c r="C3" s="1"/>
       <c r="D3" s="3" t="s">
         <v>2</v>
@@ -854,23 +854,23 @@
       <c r="K3" s="1"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
     </row>
     <row r="9" spans="1:11" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="6" t="s">
         <v>8</v>
       </c>
       <c r="D10" t="s">
@@ -887,8 +887,8 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
       <c r="D11" s="3" t="s">
         <v>2</v>
       </c>
@@ -903,23 +903,23 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
     </row>
     <row r="17" spans="1:8" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="6" t="s">
         <v>9</v>
       </c>
       <c r="D18" t="s">
@@ -936,8 +936,8 @@
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
+      <c r="A19" s="5"/>
+      <c r="B19" s="6"/>
       <c r="D19" s="3" t="s">
         <v>2</v>
       </c>
@@ -952,16 +952,16 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="6"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
     </row>
     <row r="25" spans="1:8" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="26" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -973,18 +973,18 @@
     <row r="73" ht="9.9" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="B10:B11"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="B12:B13"/>
     <mergeCell ref="A18:A19"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="A20:A21"/>
     <mergeCell ref="B20:B21"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="B10:B11"/>
   </mergeCells>
   <pageMargins left="0" right="3.937007874015748E-2" top="3.937007874015748E-2" bottom="3.937007874015748E-2" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="74" orientation="portrait" r:id="rId1"/>
